--- a/tests/fixtures/generated/e2e/varejo_teste.xlsx
+++ b/tests/fixtures/generated/e2e/varejo_teste.xlsx
@@ -458,28 +458,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F2">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="G2">
-        <v>100.38</v>
+        <v>255.43</v>
       </c>
       <c r="H2">
-        <v>6725.46</v>
+        <v>26053.86</v>
       </c>
       <c r="I2">
-        <v>3900.77</v>
+        <v>13548.01</v>
       </c>
       <c r="J2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K2" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L2">
-        <v>134.51</v>
+        <v>521.08</v>
       </c>
       <c r="M2">
-        <v>100.38</v>
+        <v>255.43</v>
       </c>
     </row>
     <row r="3">
@@ -499,28 +499,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F3">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>185.77</v>
+        <v>488.09</v>
       </c>
       <c r="H3">
-        <v>21363.55</v>
+        <v>9273.71</v>
       </c>
       <c r="I3">
-        <v>11963.59</v>
+        <v>4915.07</v>
       </c>
       <c r="J3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K3" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L3">
-        <v>427.27</v>
+        <v>185.47</v>
       </c>
       <c r="M3">
-        <v>185.77</v>
+        <v>488.09</v>
       </c>
     </row>
     <row r="4">
@@ -540,28 +540,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F4">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G4">
-        <v>135.5</v>
+        <v>382.37</v>
       </c>
       <c r="H4">
-        <v>24932</v>
+        <v>73032.67</v>
       </c>
       <c r="I4">
-        <v>9972.8</v>
+        <v>29943.39</v>
       </c>
       <c r="J4">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K4" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L4">
-        <v>498.64</v>
+        <v>1460.65</v>
       </c>
       <c r="M4">
-        <v>135.5</v>
+        <v>382.37</v>
       </c>
     </row>
     <row r="5">
@@ -581,28 +581,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F5">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>333.15</v>
+        <v>301.17</v>
       </c>
       <c r="H5">
-        <v>27651.45</v>
+        <v>10842.12</v>
       </c>
       <c r="I5">
-        <v>13272.7</v>
+        <v>4987.38</v>
       </c>
       <c r="J5">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K5" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L5">
-        <v>553.03</v>
+        <v>216.84</v>
       </c>
       <c r="M5">
-        <v>333.15</v>
+        <v>301.17</v>
       </c>
     </row>
     <row r="6">
@@ -622,28 +622,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F6">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="G6">
-        <v>118.68</v>
+        <v>470.57</v>
       </c>
       <c r="H6">
-        <v>15665.76</v>
+        <v>50350.99</v>
       </c>
       <c r="I6">
-        <v>7519.56</v>
+        <v>22154.44</v>
       </c>
       <c r="J6">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K6" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L6">
-        <v>313.32</v>
+        <v>1007.02</v>
       </c>
       <c r="M6">
-        <v>118.68</v>
+        <v>470.57</v>
       </c>
     </row>
     <row r="7">
@@ -663,28 +663,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F7">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="G7">
-        <v>117.05</v>
+        <v>34.17</v>
       </c>
       <c r="H7">
-        <v>18025.7</v>
+        <v>3348.66</v>
       </c>
       <c r="I7">
-        <v>8472.08</v>
+        <v>1239</v>
       </c>
       <c r="J7">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K7" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L7">
-        <v>360.51</v>
+        <v>66.97</v>
       </c>
       <c r="M7">
-        <v>117.05</v>
+        <v>34.17</v>
       </c>
     </row>
     <row r="8">
@@ -704,28 +704,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F8">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="G8">
-        <v>463.64</v>
+        <v>302.49</v>
       </c>
       <c r="H8">
-        <v>22254.72</v>
+        <v>49305.87</v>
       </c>
       <c r="I8">
-        <v>12240.1</v>
+        <v>19229.29</v>
       </c>
       <c r="J8">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="K8" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L8">
-        <v>445.09</v>
+        <v>986.12</v>
       </c>
       <c r="M8">
-        <v>463.64</v>
+        <v>302.49</v>
       </c>
     </row>
     <row r="9">
@@ -745,28 +745,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G9">
-        <v>346.03</v>
+        <v>421.87</v>
       </c>
       <c r="H9">
-        <v>34603</v>
+        <v>63280.5</v>
       </c>
       <c r="I9">
-        <v>15917.38</v>
+        <v>37968.3</v>
       </c>
       <c r="J9">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="K9" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L9">
-        <v>692.06</v>
+        <v>1265.61</v>
       </c>
       <c r="M9">
-        <v>346.03</v>
+        <v>421.87</v>
       </c>
     </row>
     <row r="10">
@@ -786,28 +786,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F10">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="G10">
-        <v>226.88</v>
+        <v>34.39</v>
       </c>
       <c r="H10">
-        <v>21780.48</v>
+        <v>1134.87</v>
       </c>
       <c r="I10">
-        <v>10672.44</v>
+        <v>533.39</v>
       </c>
       <c r="J10">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K10" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L10">
-        <v>435.61</v>
+        <v>22.7</v>
       </c>
       <c r="M10">
-        <v>226.88</v>
+        <v>34.39</v>
       </c>
     </row>
     <row r="11">
@@ -827,28 +827,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F11">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G11">
-        <v>438.87</v>
+        <v>250.92</v>
       </c>
       <c r="H11">
-        <v>25893.33</v>
+        <v>15807.96</v>
       </c>
       <c r="I11">
-        <v>15536</v>
+        <v>7587.82</v>
       </c>
       <c r="J11">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="K11" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L11">
-        <v>517.87</v>
+        <v>316.16</v>
       </c>
       <c r="M11">
-        <v>438.87</v>
+        <v>250.92</v>
       </c>
     </row>
     <row r="12">
@@ -868,28 +868,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F12">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="G12">
-        <v>400.57</v>
+        <v>57.36</v>
       </c>
       <c r="H12">
-        <v>61687.78</v>
+        <v>8030.4</v>
       </c>
       <c r="I12">
-        <v>33928.28</v>
+        <v>4095.5</v>
       </c>
       <c r="J12">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K12" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L12">
-        <v>1233.76</v>
+        <v>160.61</v>
       </c>
       <c r="M12">
-        <v>400.57</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="13">
@@ -909,28 +909,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F13">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="G13">
-        <v>233.31</v>
+        <v>129.17</v>
       </c>
       <c r="H13">
-        <v>41529.18</v>
+        <v>10462.77</v>
       </c>
       <c r="I13">
-        <v>21595.17</v>
+        <v>5336.01</v>
       </c>
       <c r="J13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K13" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L13">
-        <v>830.58</v>
+        <v>209.26</v>
       </c>
       <c r="M13">
-        <v>233.31</v>
+        <v>129.17</v>
       </c>
     </row>
     <row r="14">
@@ -950,28 +950,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G14">
-        <v>153.98</v>
+        <v>20.56</v>
       </c>
       <c r="H14">
-        <v>3849.5</v>
+        <v>637.36</v>
       </c>
       <c r="I14">
-        <v>1963.25</v>
+        <v>382.42</v>
       </c>
       <c r="J14">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K14" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L14">
-        <v>76.99</v>
+        <v>12.75</v>
       </c>
       <c r="M14">
-        <v>153.98</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="15">
@@ -991,28 +991,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F15">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="G15">
-        <v>275.3</v>
+        <v>260.45</v>
       </c>
       <c r="H15">
-        <v>50104.6</v>
+        <v>12501.6</v>
       </c>
       <c r="I15">
-        <v>20542.89</v>
+        <v>6750.86</v>
       </c>
       <c r="J15">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="K15" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L15">
-        <v>1002.09</v>
+        <v>250.03</v>
       </c>
       <c r="M15">
-        <v>275.3</v>
+        <v>260.45</v>
       </c>
     </row>
     <row r="16">
@@ -1032,28 +1032,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F16">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="G16">
-        <v>362.92</v>
+        <v>436.3</v>
       </c>
       <c r="H16">
-        <v>31211.12</v>
+        <v>24432.8</v>
       </c>
       <c r="I16">
-        <v>15917.67</v>
+        <v>11972.07</v>
       </c>
       <c r="J16">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K16" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L16">
-        <v>624.22</v>
+        <v>488.66</v>
       </c>
       <c r="M16">
-        <v>362.92</v>
+        <v>436.3</v>
       </c>
     </row>
     <row r="17">
@@ -1073,28 +1073,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F17">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="G17">
-        <v>479.3</v>
+        <v>106.85</v>
       </c>
       <c r="H17">
-        <v>47930</v>
+        <v>8120.6</v>
       </c>
       <c r="I17">
-        <v>20130.6</v>
+        <v>4141.51</v>
       </c>
       <c r="J17">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="K17" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L17">
-        <v>958.6</v>
+        <v>162.41</v>
       </c>
       <c r="M17">
-        <v>479.3</v>
+        <v>106.85</v>
       </c>
     </row>
     <row r="18">
@@ -1114,28 +1114,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F18">
-        <v>197</v>
+        <v>53</v>
       </c>
       <c r="G18">
-        <v>483.36</v>
+        <v>498.82</v>
       </c>
       <c r="H18">
-        <v>95221.92</v>
+        <v>26437.46</v>
       </c>
       <c r="I18">
-        <v>52372.06</v>
+        <v>10310.61</v>
       </c>
       <c r="J18">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="K18" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L18">
-        <v>1904.44</v>
+        <v>528.75</v>
       </c>
       <c r="M18">
-        <v>483.36</v>
+        <v>498.82</v>
       </c>
     </row>
     <row r="19">
@@ -1155,28 +1155,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F19">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="G19">
-        <v>332.92</v>
+        <v>464.9</v>
       </c>
       <c r="H19">
-        <v>19309.36</v>
+        <v>84611.8</v>
       </c>
       <c r="I19">
-        <v>9654.68</v>
+        <v>32998.6</v>
       </c>
       <c r="J19">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K19" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L19">
-        <v>386.19</v>
+        <v>1692.24</v>
       </c>
       <c r="M19">
-        <v>332.92</v>
+        <v>464.9</v>
       </c>
     </row>
     <row r="20">
@@ -1196,28 +1196,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F20">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G20">
-        <v>113.03</v>
+        <v>121.55</v>
       </c>
       <c r="H20">
-        <v>21814.79</v>
+        <v>23702.25</v>
       </c>
       <c r="I20">
-        <v>8944.06</v>
+        <v>10666.01</v>
       </c>
       <c r="J20">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K20" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L20">
-        <v>436.3</v>
+        <v>474.05</v>
       </c>
       <c r="M20">
-        <v>113.03</v>
+        <v>121.55</v>
       </c>
     </row>
     <row r="21">
@@ -1237,28 +1237,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F21">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="G21">
-        <v>457.06</v>
+        <v>227.13</v>
       </c>
       <c r="H21">
-        <v>7312.96</v>
+        <v>13854.93</v>
       </c>
       <c r="I21">
-        <v>3729.61</v>
+        <v>6511.82</v>
       </c>
       <c r="J21">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K21" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L21">
-        <v>146.26</v>
+        <v>277.1</v>
       </c>
       <c r="M21">
-        <v>457.06</v>
+        <v>227.13</v>
       </c>
     </row>
     <row r="22">
@@ -1278,28 +1278,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F22">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="G22">
-        <v>277.02</v>
+        <v>450.03</v>
       </c>
       <c r="H22">
-        <v>42661.08</v>
+        <v>81005.4</v>
       </c>
       <c r="I22">
-        <v>21330.54</v>
+        <v>35642.38</v>
       </c>
       <c r="J22">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K22" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L22">
-        <v>853.22</v>
+        <v>1620.11</v>
       </c>
       <c r="M22">
-        <v>277.02</v>
+        <v>450.03</v>
       </c>
     </row>
     <row r="23">
@@ -1319,28 +1319,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F23">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="G23">
-        <v>204.43</v>
+        <v>459.59</v>
       </c>
       <c r="H23">
-        <v>31277.79</v>
+        <v>11030.16</v>
       </c>
       <c r="I23">
-        <v>13762.23</v>
+        <v>4081.16</v>
       </c>
       <c r="J23">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K23" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L23">
-        <v>625.56</v>
+        <v>220.6</v>
       </c>
       <c r="M23">
-        <v>204.43</v>
+        <v>459.59</v>
       </c>
     </row>
     <row r="24">
@@ -1360,28 +1360,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F24">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G24">
-        <v>307.36</v>
+        <v>445.81</v>
       </c>
       <c r="H24">
-        <v>12294.4</v>
+        <v>7132.96</v>
       </c>
       <c r="I24">
-        <v>6147.2</v>
+        <v>3637.81</v>
       </c>
       <c r="J24">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K24" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L24">
-        <v>245.89</v>
+        <v>142.66</v>
       </c>
       <c r="M24">
-        <v>307.36</v>
+        <v>445.81</v>
       </c>
     </row>
     <row r="25">
@@ -1401,28 +1401,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F25">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="G25">
-        <v>378.81</v>
+        <v>350.99</v>
       </c>
       <c r="H25">
-        <v>67806.99</v>
+        <v>51946.52</v>
       </c>
       <c r="I25">
-        <v>31869.29</v>
+        <v>31167.91</v>
       </c>
       <c r="J25">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="K25" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L25">
-        <v>1356.14</v>
+        <v>1038.93</v>
       </c>
       <c r="M25">
-        <v>378.81</v>
+        <v>350.99</v>
       </c>
     </row>
     <row r="26">
@@ -1442,28 +1442,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F26">
-        <v>188</v>
+        <v>56</v>
       </c>
       <c r="G26">
-        <v>365.66</v>
+        <v>456.24</v>
       </c>
       <c r="H26">
-        <v>68744.08</v>
+        <v>25549.44</v>
       </c>
       <c r="I26">
-        <v>28185.07</v>
+        <v>13030.21</v>
       </c>
       <c r="J26">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="K26" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L26">
-        <v>1374.88</v>
+        <v>510.99</v>
       </c>
       <c r="M26">
-        <v>365.66</v>
+        <v>456.24</v>
       </c>
     </row>
     <row r="27">
@@ -1483,28 +1483,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F27">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="G27">
-        <v>198.11</v>
+        <v>317.83</v>
       </c>
       <c r="H27">
-        <v>37244.68</v>
+        <v>55938.08</v>
       </c>
       <c r="I27">
-        <v>21229.47</v>
+        <v>32444.09</v>
       </c>
       <c r="J27">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K27" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L27">
-        <v>744.89</v>
+        <v>1118.76</v>
       </c>
       <c r="M27">
-        <v>198.11</v>
+        <v>317.83</v>
       </c>
     </row>
     <row r="28">
@@ -1524,28 +1524,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F28">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G28">
-        <v>191.28</v>
+        <v>99.63</v>
       </c>
       <c r="H28">
-        <v>19893.12</v>
+        <v>10162.26</v>
       </c>
       <c r="I28">
-        <v>9150.84</v>
+        <v>4979.51</v>
       </c>
       <c r="J28">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K28" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L28">
-        <v>397.86</v>
+        <v>203.25</v>
       </c>
       <c r="M28">
-        <v>191.28</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="29">
@@ -1565,28 +1565,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F29">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="G29">
-        <v>321.52</v>
+        <v>282.13</v>
       </c>
       <c r="H29">
-        <v>63660.96</v>
+        <v>33291.34</v>
       </c>
       <c r="I29">
-        <v>35013.53</v>
+        <v>11984.88</v>
       </c>
       <c r="J29">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="K29" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L29">
-        <v>1273.22</v>
+        <v>665.83</v>
       </c>
       <c r="M29">
-        <v>321.52</v>
+        <v>282.13</v>
       </c>
     </row>
     <row r="30">
@@ -1606,28 +1606,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F30">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="G30">
-        <v>342.15</v>
+        <v>151.24</v>
       </c>
       <c r="H30">
-        <v>9238.05</v>
+        <v>15124</v>
       </c>
       <c r="I30">
-        <v>3418.08</v>
+        <v>6805.8</v>
       </c>
       <c r="J30">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K30" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L30">
-        <v>184.76</v>
+        <v>302.48</v>
       </c>
       <c r="M30">
-        <v>342.15</v>
+        <v>151.24</v>
       </c>
     </row>
     <row r="31">
@@ -1647,28 +1647,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F31">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G31">
-        <v>373.93</v>
+        <v>208.94</v>
       </c>
       <c r="H31">
-        <v>37766.93</v>
+        <v>18595.66</v>
       </c>
       <c r="I31">
-        <v>15484.44</v>
+        <v>10785.48</v>
       </c>
       <c r="J31">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="K31" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L31">
-        <v>755.34</v>
+        <v>371.91</v>
       </c>
       <c r="M31">
-        <v>373.93</v>
+        <v>208.94</v>
       </c>
     </row>
     <row r="32">
@@ -1688,28 +1688,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F32">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="G32">
-        <v>88.85</v>
+        <v>124.72</v>
       </c>
       <c r="H32">
-        <v>9595.8</v>
+        <v>5362.96</v>
       </c>
       <c r="I32">
-        <v>5469.61</v>
+        <v>2091.55</v>
       </c>
       <c r="J32">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="K32" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L32">
-        <v>191.92</v>
+        <v>107.26</v>
       </c>
       <c r="M32">
-        <v>88.85</v>
+        <v>124.72</v>
       </c>
     </row>
     <row r="33">
@@ -1729,28 +1729,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F33">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="G33">
-        <v>153.43</v>
+        <v>155.19</v>
       </c>
       <c r="H33">
-        <v>30379.14</v>
+        <v>12104.82</v>
       </c>
       <c r="I33">
-        <v>14581.99</v>
+        <v>5568.22</v>
       </c>
       <c r="J33">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K33" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L33">
-        <v>607.58</v>
+        <v>242.1</v>
       </c>
       <c r="M33">
-        <v>153.43</v>
+        <v>155.19</v>
       </c>
     </row>
     <row r="34">
@@ -1770,28 +1770,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F34">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="G34">
-        <v>169.46</v>
+        <v>485.93</v>
       </c>
       <c r="H34">
-        <v>25080.08</v>
+        <v>57339.74</v>
       </c>
       <c r="I34">
-        <v>11536.84</v>
+        <v>24082.69</v>
       </c>
       <c r="J34">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K34" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L34">
-        <v>501.6</v>
+        <v>1146.79</v>
       </c>
       <c r="M34">
-        <v>169.46</v>
+        <v>485.93</v>
       </c>
     </row>
     <row r="35">
@@ -1811,28 +1811,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F35">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="G35">
-        <v>63.51</v>
+        <v>173.61</v>
       </c>
       <c r="H35">
-        <v>5461.86</v>
+        <v>7291.62</v>
       </c>
       <c r="I35">
-        <v>2130.13</v>
+        <v>3062.48</v>
       </c>
       <c r="J35">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K35" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L35">
-        <v>109.24</v>
+        <v>145.83</v>
       </c>
       <c r="M35">
-        <v>63.51</v>
+        <v>173.61</v>
       </c>
     </row>
     <row r="36">
@@ -1852,28 +1852,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F36">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="G36">
-        <v>189.68</v>
+        <v>442.46</v>
       </c>
       <c r="H36">
-        <v>34142.4</v>
+        <v>16813.48</v>
       </c>
       <c r="I36">
-        <v>19461.17</v>
+        <v>6893.53</v>
       </c>
       <c r="J36">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K36" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L36">
-        <v>682.85</v>
+        <v>336.27</v>
       </c>
       <c r="M36">
-        <v>189.68</v>
+        <v>442.46</v>
       </c>
     </row>
     <row r="37">
@@ -1893,28 +1893,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F37">
-        <v>173</v>
+        <v>14</v>
       </c>
       <c r="G37">
-        <v>367.16</v>
+        <v>196.87</v>
       </c>
       <c r="H37">
-        <v>63518.68</v>
+        <v>2756.18</v>
       </c>
       <c r="I37">
-        <v>34300.09</v>
+        <v>1322.97</v>
       </c>
       <c r="J37">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K37" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L37">
-        <v>1270.37</v>
+        <v>55.12</v>
       </c>
       <c r="M37">
-        <v>367.16</v>
+        <v>196.87</v>
       </c>
     </row>
     <row r="38">
@@ -1934,28 +1934,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F38">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="G38">
-        <v>410.04</v>
+        <v>403.18</v>
       </c>
       <c r="H38">
-        <v>9840.96</v>
+        <v>59670.64</v>
       </c>
       <c r="I38">
-        <v>4723.66</v>
+        <v>27448.49</v>
       </c>
       <c r="J38">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K38" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L38">
-        <v>196.82</v>
+        <v>1193.41</v>
       </c>
       <c r="M38">
-        <v>410.04</v>
+        <v>403.18</v>
       </c>
     </row>
     <row r="39">
@@ -1975,28 +1975,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F39">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="G39">
-        <v>464.78</v>
+        <v>167.73</v>
       </c>
       <c r="H39">
-        <v>6042.14</v>
+        <v>8554.23</v>
       </c>
       <c r="I39">
-        <v>3021.07</v>
+        <v>3507.23</v>
       </c>
       <c r="J39">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K39" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L39">
-        <v>120.84</v>
+        <v>171.08</v>
       </c>
       <c r="M39">
-        <v>464.78</v>
+        <v>167.73</v>
       </c>
     </row>
     <row r="40">
@@ -2016,28 +2016,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F40">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="G40">
-        <v>424.19</v>
+        <v>430.12</v>
       </c>
       <c r="H40">
-        <v>20785.31</v>
+        <v>31398.76</v>
       </c>
       <c r="I40">
-        <v>8937.68</v>
+        <v>12559.5</v>
       </c>
       <c r="J40">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K40" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L40">
-        <v>415.71</v>
+        <v>627.98</v>
       </c>
       <c r="M40">
-        <v>424.19</v>
+        <v>430.12</v>
       </c>
     </row>
     <row r="41">
@@ -2057,28 +2057,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F41">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="G41">
-        <v>107.16</v>
+        <v>178.58</v>
       </c>
       <c r="H41">
-        <v>12966.36</v>
+        <v>10536.22</v>
       </c>
       <c r="I41">
-        <v>6872.17</v>
+        <v>6216.37</v>
       </c>
       <c r="J41">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="K41" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L41">
-        <v>259.33</v>
+        <v>210.72</v>
       </c>
       <c r="M41">
-        <v>107.16</v>
+        <v>178.58</v>
       </c>
     </row>
     <row r="42">
@@ -2098,28 +2098,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F42">
-        <v>47</v>
+        <v>195</v>
       </c>
       <c r="G42">
-        <v>459.56</v>
+        <v>45.78</v>
       </c>
       <c r="H42">
-        <v>21599.32</v>
+        <v>8927.1</v>
       </c>
       <c r="I42">
-        <v>7991.75</v>
+        <v>3570.84</v>
       </c>
       <c r="J42">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K42" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L42">
-        <v>431.99</v>
+        <v>178.54</v>
       </c>
       <c r="M42">
-        <v>459.56</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="43">
@@ -2139,28 +2139,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F43">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="G43">
-        <v>459.9</v>
+        <v>307.14</v>
       </c>
       <c r="H43">
-        <v>31733.1</v>
+        <v>54670.92</v>
       </c>
       <c r="I43">
-        <v>15549.22</v>
+        <v>21321.66</v>
       </c>
       <c r="J43">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="K43" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L43">
-        <v>634.66</v>
+        <v>1093.42</v>
       </c>
       <c r="M43">
-        <v>459.9</v>
+        <v>307.14</v>
       </c>
     </row>
     <row r="44">
@@ -2180,28 +2180,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F44">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="G44">
-        <v>483.07</v>
+        <v>150.91</v>
       </c>
       <c r="H44">
-        <v>42027.09</v>
+        <v>17505.56</v>
       </c>
       <c r="I44">
-        <v>15550.02</v>
+        <v>8752.78</v>
       </c>
       <c r="J44">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="K44" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L44">
-        <v>840.54</v>
+        <v>350.11</v>
       </c>
       <c r="M44">
-        <v>483.07</v>
+        <v>150.91</v>
       </c>
     </row>
     <row r="45">
@@ -2221,28 +2221,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F45">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="G45">
-        <v>70.63</v>
+        <v>338.07</v>
       </c>
       <c r="H45">
-        <v>7345.52</v>
+        <v>31102.44</v>
       </c>
       <c r="I45">
-        <v>3966.58</v>
+        <v>11196.88</v>
       </c>
       <c r="J45">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="K45" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L45">
-        <v>146.91</v>
+        <v>622.05</v>
       </c>
       <c r="M45">
-        <v>70.63</v>
+        <v>338.07</v>
       </c>
     </row>
     <row r="46">
@@ -2262,28 +2262,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F46">
-        <v>194</v>
+        <v>81</v>
       </c>
       <c r="G46">
-        <v>248.74</v>
+        <v>464.67</v>
       </c>
       <c r="H46">
-        <v>48255.56</v>
+        <v>37638.27</v>
       </c>
       <c r="I46">
-        <v>26058</v>
+        <v>15055.31</v>
       </c>
       <c r="J46">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="K46" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L46">
-        <v>965.11</v>
+        <v>752.77</v>
       </c>
       <c r="M46">
-        <v>248.74</v>
+        <v>464.67</v>
       </c>
     </row>
     <row r="47">
@@ -2303,28 +2303,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F47">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="G47">
-        <v>349.74</v>
+        <v>336.66</v>
       </c>
       <c r="H47">
-        <v>12240.9</v>
+        <v>60598.8</v>
       </c>
       <c r="I47">
-        <v>4284.31</v>
+        <v>26057.48</v>
       </c>
       <c r="J47">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K47" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L47">
-        <v>244.82</v>
+        <v>1211.98</v>
       </c>
       <c r="M47">
-        <v>349.74</v>
+        <v>336.66</v>
       </c>
     </row>
     <row r="48">
@@ -2344,28 +2344,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F48">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G48">
-        <v>141.33</v>
+        <v>130.81</v>
       </c>
       <c r="H48">
-        <v>9186.45</v>
+        <v>11772.9</v>
       </c>
       <c r="I48">
-        <v>5144.41</v>
+        <v>4709.16</v>
       </c>
       <c r="J48">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K48" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L48">
-        <v>183.73</v>
+        <v>235.46</v>
       </c>
       <c r="M48">
-        <v>141.33</v>
+        <v>130.81</v>
       </c>
     </row>
     <row r="49">
@@ -2385,28 +2385,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F49">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="G49">
-        <v>200.38</v>
+        <v>448.08</v>
       </c>
       <c r="H49">
-        <v>24646.74</v>
+        <v>48392.64</v>
       </c>
       <c r="I49">
-        <v>11337.5</v>
+        <v>29035.58</v>
       </c>
       <c r="J49">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="K49" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L49">
-        <v>492.93</v>
+        <v>967.85</v>
       </c>
       <c r="M49">
-        <v>200.38</v>
+        <v>448.08</v>
       </c>
     </row>
     <row r="50">
@@ -2426,28 +2426,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F50">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="G50">
-        <v>351.94</v>
+        <v>97.3</v>
       </c>
       <c r="H50">
-        <v>7742.68</v>
+        <v>15665.3</v>
       </c>
       <c r="I50">
-        <v>2942.22</v>
+        <v>9242.53</v>
       </c>
       <c r="J50">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="K50" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L50">
-        <v>154.85</v>
+        <v>313.31</v>
       </c>
       <c r="M50">
-        <v>351.94</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="51">
@@ -2467,28 +2467,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F51">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G51">
-        <v>150.78</v>
+        <v>73.64</v>
       </c>
       <c r="H51">
-        <v>26386.5</v>
+        <v>13476.12</v>
       </c>
       <c r="I51">
-        <v>10818.47</v>
+        <v>4986.16</v>
       </c>
       <c r="J51">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K51" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L51">
-        <v>527.73</v>
+        <v>269.52</v>
       </c>
       <c r="M51">
-        <v>150.78</v>
+        <v>73.64</v>
       </c>
     </row>
     <row r="52">
@@ -2508,28 +2508,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F52">
-        <v>167</v>
+        <v>26</v>
       </c>
       <c r="G52">
-        <v>301.3</v>
+        <v>494.85</v>
       </c>
       <c r="H52">
-        <v>50317.1</v>
+        <v>12866.1</v>
       </c>
       <c r="I52">
-        <v>29687.09</v>
+        <v>6561.71</v>
       </c>
       <c r="J52">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K52" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L52">
-        <v>1006.34</v>
+        <v>257.32</v>
       </c>
       <c r="M52">
-        <v>301.3</v>
+        <v>494.85</v>
       </c>
     </row>
     <row r="53">
@@ -2549,28 +2549,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F53">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="G53">
-        <v>424.53</v>
+        <v>359.27</v>
       </c>
       <c r="H53">
-        <v>19103.85</v>
+        <v>64668.6</v>
       </c>
       <c r="I53">
-        <v>7068.42</v>
+        <v>30394.24</v>
       </c>
       <c r="J53">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K53" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L53">
-        <v>382.08</v>
+        <v>1293.37</v>
       </c>
       <c r="M53">
-        <v>424.53</v>
+        <v>359.27</v>
       </c>
     </row>
     <row r="54">
@@ -2590,28 +2590,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F54">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="G54">
-        <v>489.53</v>
+        <v>398.6</v>
       </c>
       <c r="H54">
-        <v>90563.05</v>
+        <v>15944</v>
       </c>
       <c r="I54">
-        <v>39847.74</v>
+        <v>6218.16</v>
       </c>
       <c r="J54">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K54" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L54">
-        <v>1811.26</v>
+        <v>318.88</v>
       </c>
       <c r="M54">
-        <v>489.53</v>
+        <v>398.6</v>
       </c>
     </row>
     <row r="55">
@@ -2631,28 +2631,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F55">
+        <v>69</v>
+      </c>
+      <c r="G55">
+        <v>487.1</v>
+      </c>
+      <c r="H55">
+        <v>33609.9</v>
+      </c>
+      <c r="I55">
+        <v>18821.54</v>
+      </c>
+      <c r="J55">
         <v>44</v>
-      </c>
-      <c r="G55">
-        <v>139.5</v>
-      </c>
-      <c r="H55">
-        <v>6138</v>
-      </c>
-      <c r="I55">
-        <v>2823.48</v>
-      </c>
-      <c r="J55">
-        <v>54</v>
       </c>
       <c r="K55" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L55">
-        <v>122.76</v>
+        <v>672.2</v>
       </c>
       <c r="M55">
-        <v>139.5</v>
+        <v>487.1</v>
       </c>
     </row>
     <row r="56">
@@ -2672,28 +2672,28 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F56">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="G56">
-        <v>368.86</v>
+        <v>126.73</v>
       </c>
       <c r="H56">
-        <v>43525.48</v>
+        <v>12546.27</v>
       </c>
       <c r="I56">
-        <v>21327.49</v>
+        <v>7402.3</v>
       </c>
       <c r="J56">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="K56" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L56">
-        <v>870.51</v>
+        <v>250.93</v>
       </c>
       <c r="M56">
-        <v>368.86</v>
+        <v>126.73</v>
       </c>
     </row>
     <row r="57">
@@ -2713,28 +2713,28 @@
         <v>Eletrônico A</v>
       </c>
       <c r="F57">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="G57">
-        <v>120.26</v>
+        <v>246.89</v>
       </c>
       <c r="H57">
-        <v>21286.02</v>
+        <v>32095.7</v>
       </c>
       <c r="I57">
-        <v>10430.15</v>
+        <v>15084.98</v>
       </c>
       <c r="J57">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K57" t="str">
         <v>Diego Nunes</v>
       </c>
       <c r="L57">
-        <v>425.72</v>
+        <v>641.91</v>
       </c>
       <c r="M57">
-        <v>120.26</v>
+        <v>246.89</v>
       </c>
     </row>
     <row r="58">
@@ -2754,28 +2754,28 @@
         <v>Roupa B</v>
       </c>
       <c r="F58">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="G58">
-        <v>74.29</v>
+        <v>377.04</v>
       </c>
       <c r="H58">
-        <v>13075.04</v>
+        <v>31294.32</v>
       </c>
       <c r="I58">
-        <v>6537.52</v>
+        <v>13143.61</v>
       </c>
       <c r="J58">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K58" t="str">
         <v>Ana Lima</v>
       </c>
       <c r="L58">
-        <v>261.5</v>
+        <v>625.89</v>
       </c>
       <c r="M58">
-        <v>74.29</v>
+        <v>377.04</v>
       </c>
     </row>
     <row r="59">
@@ -2795,28 +2795,28 @@
         <v>Alimento C</v>
       </c>
       <c r="F59">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G59">
-        <v>434.36</v>
+        <v>130.38</v>
       </c>
       <c r="H59">
-        <v>24758.52</v>
+        <v>6910.14</v>
       </c>
       <c r="I59">
-        <v>13369.6</v>
+        <v>3385.97</v>
       </c>
       <c r="J59">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K59" t="str">
         <v>Bruno Faria</v>
       </c>
       <c r="L59">
-        <v>495.17</v>
+        <v>138.2</v>
       </c>
       <c r="M59">
-        <v>434.36</v>
+        <v>130.38</v>
       </c>
     </row>
     <row r="60">
@@ -2836,28 +2836,28 @@
         <v>Cosmético D</v>
       </c>
       <c r="F60">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G60">
-        <v>366.71</v>
+        <v>392.39</v>
       </c>
       <c r="H60">
-        <v>49872.56</v>
+        <v>46302.02</v>
       </c>
       <c r="I60">
-        <v>22442.65</v>
+        <v>26392.15</v>
       </c>
       <c r="J60">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="K60" t="str">
         <v>Carla Dias</v>
       </c>
       <c r="L60">
-        <v>997.45</v>
+        <v>926.04</v>
       </c>
       <c r="M60">
-        <v>366.71</v>
+        <v>392.39</v>
       </c>
     </row>
     <row r="61">
@@ -2877,16 +2877,16 @@
         <v>Ferramenta E</v>
       </c>
       <c r="F61">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G61">
-        <v>169.35</v>
+        <v>156.38</v>
       </c>
       <c r="H61">
-        <v>27604.05</v>
+        <v>25020.8</v>
       </c>
       <c r="I61">
-        <v>12145.78</v>
+        <v>11009.15</v>
       </c>
       <c r="J61">
         <v>56</v>
@@ -2895,10 +2895,10 @@
         <v>Diego Nunes</v>
       </c>
       <c r="L61">
-        <v>552.08</v>
+        <v>500.42</v>
       </c>
       <c r="M61">
-        <v>169.35</v>
+        <v>156.38</v>
       </c>
     </row>
   </sheetData>
@@ -2925,7 +2925,7 @@
         <v>Receita Bruta</v>
       </c>
       <c r="B2">
-        <v>1784675</v>
+        <v>1617835.55</v>
       </c>
     </row>
     <row r="3">
@@ -2933,7 +2933,7 @@
         <v>Custo Total</v>
       </c>
       <c r="B3">
-        <v>864193.19</v>
+        <v>754925.95</v>
       </c>
     </row>
     <row r="4">
@@ -2941,7 +2941,7 @@
         <v>Lucro Bruto</v>
       </c>
       <c r="B4">
-        <v>920481.81</v>
+        <v>862909.6</v>
       </c>
     </row>
     <row r="5">
@@ -2949,7 +2949,7 @@
         <v>Comissões</v>
       </c>
       <c r="B5">
-        <v>35693.5</v>
+        <v>32356.73</v>
       </c>
     </row>
   </sheetData>
